--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638F2212-CFF1-4109-A440-26EA898F9508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FB9C12-4BA2-477E-BCD9-0BF15CB34D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="210">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -663,340 +663,13 @@
   </si>
   <si>
     <t>මම කිව්වා එන්නෙයි කියලා හැබැයි ආවෙ නැ</t>
-  </si>
-  <si>
-    <t>Singlish input types covered</t>
-  </si>
-  <si>
-    <t>Evidence or rationale for the input type covered</t>
-  </si>
-  <si>
-    <t>Question forms</t>
-  </si>
-  <si>
-    <t>Inputs with punctuation marks</t>
-  </si>
-  <si>
-    <t>Romanization / Spelling Variants</t>
-  </si>
-  <si>
-    <t>Isolated English Word Insertions in Singlish</t>
-  </si>
-  <si>
-    <t>Inputs with Slang and Casual Phrasing</t>
-  </si>
-  <si>
-    <t>Evidence: “ubat dan kohomada bn?” is a question</t>
-  </si>
-  <si>
-    <t>Rationale: Uses punctuation mark “?”</t>
-  </si>
-  <si>
-    <t>Rationale: The word “Accident” is an English word inserted into Singlish sentence</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “bn”, “itin” reflect casual chat-style Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “bn” (බන්) show informal spellings</t>
-  </si>
-  <si>
-    <t>Evidence: “oya enawada ada” is asking a question (Are you coming today?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “oya” (ඔයා), “enawada” (එනවද), “ada” (අද) are romanized Sinhala forms</t>
-  </si>
-  <si>
-    <t>Evidence: “ubata theruna da” indicates a question (Did you understand?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ubata”, “theruna”, “kiyana”, “nathnam”, “aye” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: The word “explain” is an English word inserted within the Sinhala sentence</t>
-  </si>
-  <si>
-    <t>Rationale: “ubata” is informal/slang form of “උබට”</t>
-  </si>
-  <si>
-    <t>Evidence: “mokadda … me” implies a question (What is this?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mokadda” (මොකද්ද), “me” (මේ) are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “bn” is informal slang for “බං”</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “api”, “karamu”, “nathnam”, “widiyata”, “giyaoth” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “plan”, “change”, “success” are English words inserted into the sentence</t>
-  </si>
-  <si>
-    <t>Rationale: Informal conversational structure like “wenne ne” reflects casual spoken Sinhala</t>
-  </si>
-  <si>
-    <t>Evidence: “mokadda me errors tika enne” indicates a question</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mata”, “amarui”, “enne” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “system”, “use”, “errors” are English words inserted into the sentence</t>
-  </si>
-  <si>
-    <t>Rationale: “ane bn” is informal casual Sinhala expression</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mama”, “oyata”, “kiwwa”, “hariyata”, “karanna”, “eth” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: The word “ignore” is an English word inserted within the Sinhala sentence</t>
-  </si>
-  <si>
-    <t>Rationale: Conversational phrasing like “kiwwa ne” reflects informal spoken Sinhala</t>
-  </si>
-  <si>
-    <t>Command forms</t>
-  </si>
-  <si>
-    <t>Evidence: Sentence gives an instruction “Meka ikmant aran yanv metanin” (Take this quickly from here)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “Meka”, “ikmant”, “yanv”, “metanin” are romanized Sinhala with spelling variations</t>
-  </si>
-  <si>
-    <t>Evidence: “tiyenne” implies a question (Is it near the river?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “gaga” (ගඟ), “lagad” (ළඟද), “tiyenne” (තියෙන්නේ) are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Evidence: “hari da meka” is a question (Is this correct?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “hari”, “da”, “meka” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Evidence: “oyata kawadda enne” is a question (When are you coming?)</t>
-  </si>
-  <si>
-    <t>Rationale: Input contains multiple question marks “???”</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “oyata”, “kawadda”, “enne” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Evidence: “oya enawada nadda” is a yes/no question (Are you coming or not?)</t>
-  </si>
-  <si>
-    <t>Rationale: Input contains repeated question marks “??”</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “oya”, “enawada”, “nadda” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Evidence: “puluwanda” and “hari da” indicate a question</t>
-  </si>
-  <si>
-    <t>Requests</t>
-  </si>
-  <si>
-    <t>Evidence: “mata kiyanna puluwanda” is a polite request (Can you tell me…)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mata”, “kiyanna”, “puluwanda”, “meka”, “kiyala” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mama”, “kiwwa”, “ennei”, “kiyala”, “habai”, “awe” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Informal conversational phrasing like “awe ne” reflects casual spoken Sinhala</t>
-  </si>
-  <si>
-    <t>Evidence: “iwara kalada?” is a question</t>
-  </si>
-  <si>
-    <t>Evidence: “mata help ekak dhenna”, “reply karapan” are requests</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “oya”, “thiyena”, “karaganna”, “kiyala” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “assignment”, “error”, “link”, “reply” are English words</t>
-  </si>
-  <si>
-    <t>Multi-Word English Phrases in Singlish</t>
-  </si>
-  <si>
-    <t>Rationale: “Playwright automation scripts” is a multi-word English phrase</t>
-  </si>
-  <si>
-    <t>English Digital Terms in Singlish</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “link”, “README.md” are digital terms</t>
-  </si>
-  <si>
-    <t>Platform/App Names in Singlish</t>
-  </si>
-  <si>
-    <t>Rationale: “GitHub” link is included</t>
-  </si>
-  <si>
-    <t>English Abbreviations/Acronyms in Singlish</t>
-  </si>
-  <si>
-    <t>Rationale: “ASAP” is an English abbreviation</t>
-  </si>
-  <si>
-    <t>Inputs with Dates</t>
-  </si>
-  <si>
-    <t>Rationale: “2026-05-04” is a date</t>
-  </si>
-  <si>
-    <t>Inputs with Numbers and Numeric Suffixes</t>
-  </si>
-  <si>
-    <t>Rationale: “1500k”, “100%” include numbers</t>
-  </si>
-  <si>
-    <t>Inputs with Currency</t>
-  </si>
-  <si>
-    <t>Rationale: “Rs.1500k” indicates currency</t>
-  </si>
-  <si>
-    <t>Online Identifiers in Singlish</t>
-  </si>
-  <si>
-    <t>Rationale: “@Saman” and URL are online identifiers</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ado machan”, “ban”, “hode” are casual slang</t>
-  </si>
-  <si>
-    <t>Evidence: “Hina wenna epa” is an instruction (Don’t laugh)</t>
-  </si>
-  <si>
-    <t>Rationale: Input contains mixed punctuation “!..”</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “Hina”, “wenna”, “epa” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mata”, “enne”, “be” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “ban” is informal slang for “බං”</t>
-  </si>
-  <si>
-    <t>Evidence: “yamu da nathnam inne da” is a choice question (Shall we go or stay?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “api”, “yamu”, “nathnam”, “inne” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “famasiye”, “pettiya”, “barayi” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “10kg” includes a numeric value</t>
-  </si>
-  <si>
-    <t>Inputs with Unit of Measurements</t>
-  </si>
-  <si>
-    <t>Rationale: “kg” represents a unit of weight</t>
-  </si>
-  <si>
-    <t>Rationale: Input contains a period “.”</t>
-  </si>
-  <si>
-    <t>Evidence: “theruna da” indicates a question (Did you understand?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ubata”, “theruna” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “machn” is informal slang for “මචං”</t>
-  </si>
-  <si>
-    <t>Evidence: “eka hariyata karapan” is an instruction (Do it properly)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “eka”, “hariyata”, “karapan” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “ane bn” is informal Sinhala slang expression</t>
-  </si>
-  <si>
-    <t>Evidence: “mokadda … hitan inne” implies a question</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mokadda”, “kiyald”, “hitan inne”, “dan” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: The word “seen” is an English word inserted into the sentence</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ban”, “u pora” reflect informal slang usage</t>
-  </si>
-  <si>
-    <t>Rationale: “bday” is a shortened form of “birthday”</t>
-  </si>
-  <si>
-    <t>Rationale: “eka” is romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “May 1st” represents a date</t>
-  </si>
-  <si>
-    <t>Rationale: Input ends with a period “.”</t>
-  </si>
-  <si>
-    <t>Evidence: “pissuda” implies a question (Are you crazy?)</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ubat”, “pissuda” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “mara”, “amarui”, “meka”, “karanna” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “bn” and “mara” reflect informal casual Sinhala expressions</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “elakiri”, “machan” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “elakiri” and “machan” are informal slang expressions</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ubata”, “kiyala”, “wedak”, “ne” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “www.lms.sliit.lk” is a website URL</t>
-  </si>
-  <si>
-    <t>Rationale: “details” is a common English digital/contextual term</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “thiyenne”, “eke” are romanized Sinhala</t>
-  </si>
-  <si>
-    <t>Rationale: “password” is a common digital term</t>
-  </si>
-  <si>
-    <t>Rationale: Words like “ohet”, “eka”, “mathakei” are romanized Sinhala</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1061,13 +734,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1077,7 +743,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1157,24 +823,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1188,54 +841,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1243,31 +864,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1548,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -1556,12 +1188,10 @@
     <col min="3" max="3" width="22.109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="37.88671875" customWidth="1"/>
-    <col min="8" max="8" width="58.33203125" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="7" max="8" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,3147 +1210,2529 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="22"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="22"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="22"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="23"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-    </row>
-    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="29"/>
+    </row>
+    <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-    </row>
-    <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
-      <c r="G13" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
-      <c r="G17" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-    </row>
-    <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
-      <c r="B20" s="26"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
-      <c r="B21" s="26"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
-      <c r="G21" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
-      <c r="B22" s="27"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-    </row>
-    <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+    </row>
+    <row r="23" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H23" s="35" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
-      <c r="B24" s="26"/>
+      <c r="B24" s="14"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
-      <c r="B25" s="26"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
-      <c r="B26" s="27"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="G26" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+    </row>
+    <row r="27" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
-      <c r="B28" s="28"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
-      <c r="B29" s="28"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
-      <c r="B30" s="29"/>
+      <c r="B30" s="19"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-    </row>
-    <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+    </row>
+    <row r="31" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F31" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G31" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="H31" s="35" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
-      <c r="B32" s="26"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
-      <c r="B33" s="26"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-    </row>
-    <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
-      <c r="B34" s="27"/>
+      <c r="B34" s="15"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-    </row>
-    <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H35" s="35" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F35" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
-      <c r="B36" s="26"/>
+      <c r="B36" s="14"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
-      <c r="G36" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H36" s="35" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
-      <c r="B37" s="26"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-    </row>
-    <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="B38" s="27"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-    </row>
-    <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-    </row>
-    <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-    </row>
-    <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+    </row>
+    <row r="43" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="H43" s="33" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F43" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
-      <c r="G44" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="H44" s="33" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
-      <c r="G45" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="H45" s="33" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-    </row>
-    <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
+    </row>
+    <row r="47" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="F47" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H47" s="35" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H48" s="35" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
-      <c r="G49" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H49" s="35" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-    </row>
-    <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+    </row>
+    <row r="51" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="F51" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G51" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H51" s="35" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F51" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
-      <c r="B52" s="26"/>
+      <c r="B52" s="14"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="H52" s="35" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
-      <c r="B53" s="26"/>
+      <c r="B53" s="14"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H53" s="35" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
-      <c r="B54" s="27"/>
+      <c r="B54" s="15"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H54" s="35" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
+    </row>
+    <row r="55" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="E55" s="16" t="s">
+      <c r="E55" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="F55" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G55" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H55" s="35" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F55" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
-      <c r="G56" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H56" s="35" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-    </row>
-    <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-    </row>
-    <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
+    </row>
+    <row r="59" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="F59" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H59" s="35" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F59" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
-      <c r="G60" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="H60" s="35" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
-      <c r="G61" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H61" s="35" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
-      <c r="G62" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H62" s="35" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
-      <c r="G63" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="H63" s="35" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
-      <c r="G64" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="H64" s="35" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
-      <c r="G65" s="35" t="s">
-        <v>268</v>
-      </c>
-      <c r="H65" s="35" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
-      <c r="G66" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="H66" s="35" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
-      <c r="G67" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
-      <c r="G68" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
-      <c r="G69" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="H69" s="35" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
-      <c r="G70" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H70" s="35" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="H71" s="35" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="11" t="s">
+    </row>
+    <row r="72" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="E72" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F72" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G72" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="H72" s="35" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F72" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
-      <c r="B73" s="26"/>
+      <c r="B73" s="14"/>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
-      <c r="G73" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H73" s="35" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
-      <c r="B74" s="26"/>
+      <c r="B74" s="14"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
-      <c r="G74" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H74" s="35" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
-      <c r="B75" s="27"/>
+      <c r="B75" s="15"/>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-    </row>
-    <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
+    </row>
+    <row r="76" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B76" s="17" t="s">
+      <c r="B76" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="16" t="s">
+      <c r="E76" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F76" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G76" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H76" s="35" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F76" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
-      <c r="G77" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H77" s="35" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-    </row>
-    <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-    </row>
-    <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
+    </row>
+    <row r="80" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E80" s="16" t="s">
+      <c r="E80" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F80" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G80" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H80" s="35" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F80" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
-      <c r="G81" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H81" s="35" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
-      <c r="G82" s="30"/>
-      <c r="H82" s="30"/>
-    </row>
-    <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
-      <c r="G83" s="30"/>
-      <c r="H83" s="30"/>
-    </row>
-    <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="11" t="s">
+    </row>
+    <row r="84" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="E84" s="16" t="s">
+      <c r="E84" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="F84" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G84" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H84" s="35" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F84" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
-      <c r="G85" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="H85" s="35" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
-      <c r="G86" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="H86" s="35" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
-      <c r="G87" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H87" s="35" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="11" t="s">
+    </row>
+    <row r="88" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B88" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E88" s="16" t="s">
+      <c r="E88" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F88" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G88" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H88" s="35" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F88" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
-      <c r="G89" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H89" s="35" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
-      <c r="G90" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H90" s="35" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
-    </row>
-    <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="11" t="s">
+    </row>
+    <row r="92" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="16" t="s">
+      <c r="E92" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F92" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G92" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="H92" s="35" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F92" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
-      <c r="G93" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H93" s="35" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
-      <c r="G94" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H94" s="35" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-    </row>
-    <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="11" t="s">
+    </row>
+    <row r="96" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E96" s="16" t="s">
+      <c r="E96" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="F96" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H96" s="35" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F96" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
-      <c r="C97" s="24"/>
-      <c r="D97" s="24"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H97" s="35" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="23"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
-      <c r="G98" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H98" s="35" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="25"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="24"/>
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
-      <c r="G99" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H99" s="35" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="11" t="s">
+    </row>
+    <row r="100" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B100" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E100" s="16" t="s">
+      <c r="E100" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F100" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="H100" s="35" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F100" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
-      <c r="G101" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H101" s="35" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
-      <c r="G102" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="H102" s="35" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
       <c r="F103" s="9"/>
-      <c r="G103" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H103" s="35" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="11" t="s">
+    </row>
+    <row r="104" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="17" t="s">
+      <c r="B104" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D104" s="15" t="s">
+      <c r="D104" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="E104" s="16" t="s">
+      <c r="E104" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F104" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G104" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="H104" s="35" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F104" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
-      <c r="G105" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H105" s="35" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
-      <c r="G106" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H106" s="35" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="30"/>
-    </row>
-    <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="11" t="s">
+    </row>
+    <row r="108" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D108" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E108" s="16" t="s">
+      <c r="E108" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F108" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G108" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H108" s="35" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F108" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
-      <c r="G109" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H109" s="35" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
-      <c r="G110" s="30"/>
-      <c r="H110" s="30"/>
-    </row>
-    <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
-      <c r="G111" s="30"/>
-      <c r="H111" s="30"/>
-    </row>
-    <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="11" t="s">
+    </row>
+    <row r="112" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D112" s="15" t="s">
+      <c r="D112" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E112" s="16" t="s">
+      <c r="E112" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="F112" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G112" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H112" s="35" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F112" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
-      <c r="G113" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H113" s="35" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
-      <c r="G114" s="30"/>
-      <c r="H114" s="30"/>
-    </row>
-    <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
-      <c r="G115" s="30"/>
-      <c r="H115" s="30"/>
-    </row>
-    <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="11" t="s">
+    </row>
+    <row r="116" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B116" s="17" t="s">
+      <c r="B116" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C116" s="14" t="s">
+      <c r="C116" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D116" s="15" t="s">
+      <c r="D116" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E116" s="16" t="s">
+      <c r="E116" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F116" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G116" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H116" s="35" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F116" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
-      <c r="G117" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="H117" s="35" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
-      <c r="G118" s="30"/>
-      <c r="H118" s="30"/>
-    </row>
-    <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
-      <c r="G119" s="30"/>
-      <c r="H119" s="30"/>
-    </row>
-    <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="11" t="s">
+    </row>
+    <row r="120" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B120" s="17" t="s">
+      <c r="B120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="E120" s="16" t="s">
+      <c r="E120" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F120" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G120" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="H120" s="35" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F120" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
-      <c r="G121" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="H121" s="35" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
-      <c r="G122" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="H122" s="35" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
-      <c r="G123" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H123" s="35" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="11" t="s">
+    </row>
+    <row r="124" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="E124" s="16" t="s">
+      <c r="E124" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="F124" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G124" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="H124" s="33" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F124" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
-      <c r="G125" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="H125" s="33" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
-      <c r="G126" s="30"/>
-      <c r="H126" s="30"/>
-    </row>
-    <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
       <c r="F127" s="9"/>
-      <c r="G127" s="30"/>
-      <c r="H127" s="30"/>
-    </row>
-    <row r="128" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="11" t="s">
+    </row>
+    <row r="128" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B128" s="17" t="s">
+      <c r="B128" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D128" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="E128" s="16" t="s">
+      <c r="E128" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F128" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G128" s="30"/>
-      <c r="H128" s="30"/>
-    </row>
-    <row r="129" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F128" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
-      <c r="G129" s="30"/>
-      <c r="H129" s="30"/>
-    </row>
-    <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
-      <c r="G130" s="30"/>
-      <c r="H130" s="30"/>
-    </row>
-    <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
-      <c r="G131" s="30"/>
-      <c r="H131" s="30"/>
-    </row>
-    <row r="132" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="11" t="s">
+    </row>
+    <row r="132" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B132" s="17" t="s">
+      <c r="B132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C132" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D132" s="13" t="s">
+      <c r="D132" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="E132" s="16" t="s">
+      <c r="E132" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="F132" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G132" s="30"/>
-      <c r="H132" s="30"/>
-    </row>
-    <row r="133" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F132" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
-      <c r="G133" s="30"/>
-      <c r="H133" s="30"/>
-    </row>
-    <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
-      <c r="G134" s="30"/>
-      <c r="H134" s="30"/>
-    </row>
-    <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
       <c r="F135" s="9"/>
-      <c r="G135" s="30"/>
-      <c r="H135" s="30"/>
-    </row>
-    <row r="136" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="11" t="s">
+    </row>
+    <row r="136" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B136" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C136" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D136" s="13" t="s">
+      <c r="D136" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="E136" s="16" t="s">
+      <c r="E136" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="F136" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G136" s="30"/>
-      <c r="H136" s="30"/>
-    </row>
-    <row r="137" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F136" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
-      <c r="G137" s="30"/>
-      <c r="H137" s="30"/>
-    </row>
-    <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
-      <c r="G138" s="30"/>
-      <c r="H138" s="30"/>
-    </row>
-    <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
       <c r="F139" s="9"/>
-      <c r="G139" s="30"/>
-      <c r="H139" s="30"/>
-    </row>
-    <row r="140" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="11" t="s">
+    </row>
+    <row r="140" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B140" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C140" s="14" t="s">
+      <c r="C140" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D140" s="15" t="s">
+      <c r="D140" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="E140" s="16" t="s">
+      <c r="E140" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="F140" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G140" s="30"/>
-      <c r="H140" s="30"/>
-    </row>
-    <row r="141" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F140" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
-      <c r="G141" s="30"/>
-      <c r="H141" s="30"/>
-    </row>
-    <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
-      <c r="G142" s="30"/>
-      <c r="H142" s="30"/>
-    </row>
-    <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
       <c r="F143" s="9"/>
-      <c r="G143" s="30"/>
-      <c r="H143" s="30"/>
-    </row>
-    <row r="144" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="11" t="s">
+    </row>
+    <row r="144" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B144" s="17" t="s">
+      <c r="B144" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D144" s="15" t="s">
+      <c r="D144" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="E144" s="16" t="s">
+      <c r="E144" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F144" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G144" s="30"/>
-      <c r="H144" s="30"/>
-    </row>
-    <row r="145" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F144" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
-      <c r="C145" s="24"/>
+      <c r="C145" s="23"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
-      <c r="G145" s="30"/>
-      <c r="H145" s="30"/>
-    </row>
-    <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
-      <c r="C146" s="24"/>
+      <c r="C146" s="23"/>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
-      <c r="G146" s="30"/>
-      <c r="H146" s="30"/>
-    </row>
-    <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
-      <c r="C147" s="25"/>
+      <c r="C147" s="24"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
-      <c r="G147" s="30"/>
-      <c r="H147" s="30"/>
-    </row>
-    <row r="148" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="11" t="s">
+    </row>
+    <row r="148" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B148" s="17" t="s">
+      <c r="B148" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C148" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D148" s="15" t="s">
+      <c r="D148" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E148" s="16" t="s">
+      <c r="E148" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="F148" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G148" s="30"/>
-      <c r="H148" s="30"/>
-    </row>
-    <row r="149" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F148" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
-      <c r="C149" s="24"/>
+      <c r="C149" s="23"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
-      <c r="G149" s="30"/>
-      <c r="H149" s="30"/>
-    </row>
-    <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
-      <c r="C150" s="24"/>
+      <c r="C150" s="23"/>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-    </row>
-    <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
-      <c r="C151" s="25"/>
+      <c r="C151" s="24"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
-      <c r="G151" s="30"/>
-      <c r="H151" s="30"/>
-    </row>
-    <row r="152" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="11" t="s">
+    </row>
+    <row r="152" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B152" s="17" t="s">
+      <c r="B152" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D152" s="15" t="s">
+      <c r="D152" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E152" s="16" t="s">
+      <c r="E152" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="F152" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G152" s="30"/>
-      <c r="H152" s="30"/>
-    </row>
-    <row r="153" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F152" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
-      <c r="G153" s="30"/>
-      <c r="H153" s="30"/>
-    </row>
-    <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
-      <c r="G154" s="30"/>
-      <c r="H154" s="30"/>
-    </row>
-    <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
-      <c r="G155" s="30"/>
-      <c r="H155" s="30"/>
-    </row>
-    <row r="156" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="11" t="s">
+    </row>
+    <row r="156" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B156" s="17" t="s">
+      <c r="B156" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C156" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D156" s="13" t="s">
+      <c r="D156" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E156" s="16" t="s">
+      <c r="E156" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F156" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G156" s="30"/>
-      <c r="H156" s="30"/>
-    </row>
-    <row r="157" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F156" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
-      <c r="G157" s="30"/>
-      <c r="H157" s="30"/>
-    </row>
-    <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
       <c r="D158" s="8"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
-      <c r="G158" s="30"/>
-      <c r="H158" s="30"/>
-    </row>
-    <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
       <c r="F159" s="9"/>
-      <c r="G159" s="30"/>
-      <c r="H159" s="30"/>
-    </row>
-    <row r="160" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="11" t="s">
+    </row>
+    <row r="160" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B160" s="17" t="s">
+      <c r="B160" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C160" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D160" s="13" t="s">
+      <c r="D160" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="E160" s="16" t="s">
+      <c r="E160" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F160" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G160" s="30"/>
-      <c r="H160" s="30"/>
-    </row>
-    <row r="161" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F160" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
-      <c r="G161" s="30"/>
-      <c r="H161" s="30"/>
-    </row>
-    <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
-      <c r="G162" s="30"/>
-      <c r="H162" s="30"/>
-    </row>
-    <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
       <c r="F163" s="9"/>
-      <c r="G163" s="30"/>
-      <c r="H163" s="30"/>
-    </row>
-    <row r="164" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="11" t="s">
+    </row>
+    <row r="164" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B164" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C164" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D164" s="13" t="s">
+      <c r="D164" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="E164" s="16" t="s">
+      <c r="E164" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="F164" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G164" s="30"/>
-      <c r="H164" s="30"/>
-    </row>
-    <row r="165" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F164" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
-      <c r="G165" s="30"/>
-      <c r="H165" s="30"/>
-    </row>
-    <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
-      <c r="G166" s="30"/>
-      <c r="H166" s="30"/>
-    </row>
-    <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
       <c r="F167" s="9"/>
-      <c r="G167" s="30"/>
-      <c r="H167" s="30"/>
-    </row>
-    <row r="168" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="11" t="s">
+    </row>
+    <row r="168" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C168" s="14" t="s">
+      <c r="C168" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D168" s="15" t="s">
+      <c r="D168" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E168" s="16" t="s">
+      <c r="E168" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="F168" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G168" s="30"/>
-      <c r="H168" s="30"/>
-    </row>
-    <row r="169" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F168" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
-      <c r="G169" s="30"/>
-      <c r="H169" s="30"/>
-    </row>
-    <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
-      <c r="G170" s="30"/>
-      <c r="H170" s="30"/>
-    </row>
-    <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
-      <c r="G171" s="30"/>
-      <c r="H171" s="30"/>
-    </row>
-    <row r="172" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="11" t="s">
+    </row>
+    <row r="172" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B172" s="17" t="s">
+      <c r="B172" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C172" s="14" t="s">
+      <c r="C172" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D172" s="15" t="s">
+      <c r="D172" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E172" s="16" t="s">
+      <c r="E172" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="F172" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G172" s="30"/>
-      <c r="H172" s="30"/>
-    </row>
-    <row r="173" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F172" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
-      <c r="G173" s="30"/>
-      <c r="H173" s="30"/>
-    </row>
-    <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
-      <c r="G174" s="30"/>
-      <c r="H174" s="30"/>
-    </row>
-    <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="9"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
-      <c r="G175" s="30"/>
-      <c r="H175" s="30"/>
-    </row>
-    <row r="176" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="11" t="s">
+    </row>
+    <row r="176" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B176" s="17" t="s">
+      <c r="B176" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C176" s="10" t="s">
+      <c r="C176" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D176" s="13" t="s">
+      <c r="D176" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="E176" s="16" t="s">
+      <c r="E176" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="F176" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G176" s="30"/>
-      <c r="H176" s="30"/>
-    </row>
-    <row r="177" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F176" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
-      <c r="G177" s="30"/>
-      <c r="H177" s="30"/>
-    </row>
-    <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="8"/>
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
-      <c r="G178" s="30"/>
-      <c r="H178" s="30"/>
-    </row>
-    <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
-      <c r="G179" s="30"/>
-      <c r="H179" s="30"/>
-    </row>
-    <row r="180" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="11" t="s">
+    </row>
+    <row r="180" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B180" s="17" t="s">
+      <c r="B180" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C180" s="14" t="s">
+      <c r="C180" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D180" s="15" t="s">
+      <c r="D180" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E180" s="20" t="s">
+      <c r="E180" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="F180" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G180" s="30"/>
-      <c r="H180" s="30"/>
-    </row>
-    <row r="181" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F180" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
       <c r="D181" s="8"/>
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
-      <c r="G181" s="30"/>
-      <c r="H181" s="30"/>
-    </row>
-    <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="8"/>
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
-      <c r="G182" s="30"/>
-      <c r="H182" s="30"/>
-    </row>
-    <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="9"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
-      <c r="G183" s="30"/>
-      <c r="H183" s="30"/>
-    </row>
-    <row r="184" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="11" t="s">
+    </row>
+    <row r="184" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B184" s="17" t="s">
+      <c r="B184" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C184" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D184" s="13" t="s">
+      <c r="D184" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E184" s="16" t="s">
+      <c r="E184" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="F184" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G184" s="30"/>
-      <c r="H184" s="30"/>
-    </row>
-    <row r="185" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F184" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
-      <c r="G185" s="30"/>
-      <c r="H185" s="30"/>
-    </row>
-    <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
-      <c r="G186" s="30"/>
-      <c r="H186" s="30"/>
-    </row>
-    <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
-      <c r="G187" s="30"/>
-      <c r="H187" s="30"/>
-    </row>
-    <row r="188" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="11" t="s">
+    </row>
+    <row r="188" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B188" s="17" t="s">
+      <c r="B188" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C188" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D188" s="13" t="s">
+      <c r="D188" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E188" s="16" t="s">
+      <c r="E188" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="F188" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G188" s="30"/>
-      <c r="H188" s="30"/>
-    </row>
-    <row r="189" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F188" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
-      <c r="G189" s="30"/>
-      <c r="H189" s="30"/>
-    </row>
-    <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
-      <c r="G190" s="30"/>
-      <c r="H190" s="30"/>
-    </row>
-    <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
-      <c r="G191" s="30"/>
-      <c r="H191" s="30"/>
-    </row>
-    <row r="192" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="11" t="s">
+    </row>
+    <row r="192" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B192" s="17" t="s">
+      <c r="B192" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="C192" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D192" s="13" t="s">
+      <c r="D192" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="E192" s="16" t="s">
+      <c r="E192" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="F192" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G192" s="30"/>
-      <c r="H192" s="30"/>
-    </row>
-    <row r="193" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F192" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
-      <c r="G193" s="30"/>
-      <c r="H193" s="30"/>
-    </row>
-    <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="8"/>
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
-      <c r="G194" s="30"/>
-      <c r="H194" s="30"/>
-    </row>
-    <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
-      <c r="G195" s="30"/>
-      <c r="H195" s="30"/>
-    </row>
-    <row r="196" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="11" t="s">
+    </row>
+    <row r="196" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B196" s="17" t="s">
+      <c r="B196" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C196" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D196" s="13" t="s">
+      <c r="D196" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="E196" s="16" t="s">
+      <c r="E196" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="F196" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G196" s="30"/>
-      <c r="H196" s="30"/>
-    </row>
-    <row r="197" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F196" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
-      <c r="G197" s="30"/>
-      <c r="H197" s="30"/>
-    </row>
-    <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="8"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
       <c r="D198" s="8"/>
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
-      <c r="G198" s="30"/>
-      <c r="H198" s="30"/>
-    </row>
-    <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
-      <c r="G199" s="30"/>
-      <c r="H199" s="30"/>
-    </row>
-    <row r="200" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="11" t="s">
+    </row>
+    <row r="200" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B200" s="17" t="s">
+      <c r="B200" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C200" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="D200" s="13" t="s">
+      <c r="D200" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E200" s="16" t="s">
+      <c r="E200" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="F200" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G200" s="30"/>
-      <c r="H200" s="30"/>
-    </row>
-    <row r="201" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F200" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
-      <c r="G201" s="30"/>
-      <c r="H201" s="30"/>
-    </row>
-    <row r="202" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="8"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
-      <c r="G202" s="30"/>
-      <c r="H202" s="30"/>
-    </row>
-    <row r="203" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
       <c r="E203" s="9"/>
       <c r="F203" s="9"/>
-      <c r="G203" s="30"/>
-      <c r="H203" s="30"/>
-    </row>
-    <row r="204" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="11" t="s">
+    </row>
+    <row r="204" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B204" s="17" t="s">
+      <c r="B204" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C204" s="10" t="s">
+      <c r="C204" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D204" s="13" t="s">
+      <c r="D204" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E204" s="16" t="s">
+      <c r="E204" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="F204" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G204" s="30"/>
-      <c r="H204" s="30"/>
-    </row>
-    <row r="205" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F204" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="8"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
-      <c r="G205" s="30"/>
-      <c r="H205" s="30"/>
-    </row>
-    <row r="206" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
-      <c r="G206" s="30"/>
-      <c r="H206" s="30"/>
-    </row>
-    <row r="207" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="9"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
       <c r="E207" s="9"/>
       <c r="F207" s="9"/>
-      <c r="G207" s="30"/>
-      <c r="H207" s="30"/>
-    </row>
-    <row r="208" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="11" t="s">
+    </row>
+    <row r="208" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B208" s="17" t="s">
+      <c r="B208" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C208" s="10" t="s">
+      <c r="C208" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="D208" s="13" t="s">
+      <c r="D208" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E208" s="16" t="s">
+      <c r="E208" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="F208" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G208" s="30"/>
-      <c r="H208" s="30"/>
-    </row>
-    <row r="209" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F208" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
       <c r="D209" s="8"/>
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
-      <c r="G209" s="30"/>
-      <c r="H209" s="30"/>
-    </row>
-    <row r="210" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
       <c r="D210" s="8"/>
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
-      <c r="G210" s="30"/>
-      <c r="H210" s="30"/>
-    </row>
-    <row r="211" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="9"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
       <c r="E211" s="9"/>
       <c r="F211" s="9"/>
-      <c r="G211" s="30"/>
-      <c r="H211" s="30"/>
-    </row>
-    <row r="212" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G212" s="30"/>
-    </row>
-    <row r="213" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G213" s="31"/>
-    </row>
-    <row r="214" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G214" s="31"/>
-    </row>
-    <row r="215" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G215" s="31"/>
-    </row>
-    <row r="216" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G216" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="301">
-    <mergeCell ref="G213:G216"/>
-    <mergeCell ref="A128:A131"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C108:C111"/>
-    <mergeCell ref="C164:C167"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="E15:E18"/>
-    <mergeCell ref="A176:A179"/>
-    <mergeCell ref="E112:E115"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="A172:A175"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="D208:D211"/>
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="A156:A159"/>
-    <mergeCell ref="F208:F211"/>
-    <mergeCell ref="C156:C159"/>
-    <mergeCell ref="D184:D187"/>
-    <mergeCell ref="F184:F187"/>
-    <mergeCell ref="A188:A191"/>
-    <mergeCell ref="C104:C107"/>
-    <mergeCell ref="D136:D139"/>
-    <mergeCell ref="E104:E107"/>
-    <mergeCell ref="F136:F139"/>
-    <mergeCell ref="D176:D179"/>
-    <mergeCell ref="E100:E103"/>
-    <mergeCell ref="F120:F123"/>
-    <mergeCell ref="D160:D163"/>
-    <mergeCell ref="F160:F163"/>
-    <mergeCell ref="E168:E171"/>
-    <mergeCell ref="B176:B179"/>
-    <mergeCell ref="B128:B131"/>
-    <mergeCell ref="F104:F107"/>
-    <mergeCell ref="E120:E123"/>
-    <mergeCell ref="F108:F111"/>
-    <mergeCell ref="E140:E143"/>
+  <mergeCells count="300">
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="A108:A111"/>
+    <mergeCell ref="F204:F207"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="C208:C211"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D132:D135"/>
+    <mergeCell ref="F132:F135"/>
+    <mergeCell ref="A136:A139"/>
+    <mergeCell ref="C140:C143"/>
+    <mergeCell ref="D172:D175"/>
+    <mergeCell ref="C192:C195"/>
+    <mergeCell ref="A152:A155"/>
+    <mergeCell ref="E192:E195"/>
+    <mergeCell ref="C120:C123"/>
+    <mergeCell ref="F116:F119"/>
+    <mergeCell ref="F196:F199"/>
+    <mergeCell ref="C160:C163"/>
+    <mergeCell ref="A200:A203"/>
+    <mergeCell ref="C200:C203"/>
+    <mergeCell ref="B124:B127"/>
+    <mergeCell ref="D124:D127"/>
+    <mergeCell ref="B164:B167"/>
+    <mergeCell ref="C184:C187"/>
+    <mergeCell ref="F180:F183"/>
+    <mergeCell ref="B148:B151"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="D200:D203"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="E92:E95"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="B192:B195"/>
+    <mergeCell ref="B188:B191"/>
+    <mergeCell ref="E172:E175"/>
+    <mergeCell ref="F140:F143"/>
+    <mergeCell ref="F55:F58"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="F164:F167"/>
+    <mergeCell ref="D196:D199"/>
+    <mergeCell ref="E176:E179"/>
+    <mergeCell ref="F200:F203"/>
+    <mergeCell ref="C188:C191"/>
+    <mergeCell ref="E188:E191"/>
+    <mergeCell ref="F172:F175"/>
+    <mergeCell ref="C176:C179"/>
+    <mergeCell ref="A148:A151"/>
+    <mergeCell ref="F96:F99"/>
+    <mergeCell ref="F152:F155"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="E108:E111"/>
+    <mergeCell ref="F80:F83"/>
+    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="D144:D147"/>
+    <mergeCell ref="F144:F147"/>
+    <mergeCell ref="E72:E75"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="E96:E99"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="F51:F54"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="D140:D143"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C204:C207"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D59:D71"/>
+    <mergeCell ref="F59:F71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="C132:C135"/>
+    <mergeCell ref="C88:C91"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="C196:C199"/>
+    <mergeCell ref="D104:D107"/>
+    <mergeCell ref="E152:E155"/>
+    <mergeCell ref="E204:E207"/>
+    <mergeCell ref="B160:B163"/>
+    <mergeCell ref="A124:A127"/>
+    <mergeCell ref="A180:A183"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="F88:F91"/>
+    <mergeCell ref="C180:C183"/>
+    <mergeCell ref="F128:F131"/>
+    <mergeCell ref="F168:F171"/>
+    <mergeCell ref="B200:B203"/>
+    <mergeCell ref="D204:D207"/>
+    <mergeCell ref="A144:A147"/>
+    <mergeCell ref="B172:B175"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E19:E22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="E144:E147"/>
+    <mergeCell ref="D148:D151"/>
+    <mergeCell ref="C168:C171"/>
+    <mergeCell ref="C128:C131"/>
+    <mergeCell ref="A168:A171"/>
+    <mergeCell ref="B156:B159"/>
+    <mergeCell ref="D156:D159"/>
+    <mergeCell ref="C59:C71"/>
+    <mergeCell ref="E59:E71"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="E148:E151"/>
+    <mergeCell ref="D168:D171"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="B144:B147"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="F148:F151"/>
+    <mergeCell ref="C152:C155"/>
+    <mergeCell ref="F100:F103"/>
+    <mergeCell ref="E128:E131"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="D116:D119"/>
+    <mergeCell ref="F76:F79"/>
+    <mergeCell ref="D19:D22"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="C148:C151"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="E55:E58"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="D128:D131"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="E136:E139"/>
+    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="A116:A119"/>
+    <mergeCell ref="F15:F18"/>
+    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B136:B139"/>
+    <mergeCell ref="D192:D195"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="A140:A143"/>
+    <mergeCell ref="F192:F195"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="B120:B123"/>
+    <mergeCell ref="E116:E119"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="D120:D123"/>
+    <mergeCell ref="A59:A71"/>
+    <mergeCell ref="E156:E159"/>
+    <mergeCell ref="F176:F179"/>
+    <mergeCell ref="E208:E211"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="C136:C139"/>
+    <mergeCell ref="E200:E203"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="F124:F127"/>
+    <mergeCell ref="D164:D167"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="E132:E135"/>
+    <mergeCell ref="E88:E91"/>
+    <mergeCell ref="B180:B183"/>
+    <mergeCell ref="B196:B199"/>
+    <mergeCell ref="B152:B155"/>
+    <mergeCell ref="D152:D155"/>
+    <mergeCell ref="E184:E187"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="C172:C175"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="E51:E54"/>
+    <mergeCell ref="D92:D95"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="F92:F95"/>
+    <mergeCell ref="A184:A187"/>
+    <mergeCell ref="D180:D183"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="B59:B71"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="C144:C147"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C124:C127"/>
+    <mergeCell ref="E31:E34"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="E124:E127"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="F112:F115"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B168:B171"/>
+    <mergeCell ref="E164:E167"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="C92:C95"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="B204:B207"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="D51:D54"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="A104:A107"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="F156:F159"/>
+    <mergeCell ref="E160:E163"/>
+    <mergeCell ref="D188:D191"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="F188:F191"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="F35:F38"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="F84:F87"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="B116:B119"/>
+    <mergeCell ref="E196:E199"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="E180:E183"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A160:A163"/>
@@ -4745,246 +3757,42 @@
     <mergeCell ref="E84:E87"/>
     <mergeCell ref="B88:B91"/>
     <mergeCell ref="D88:D91"/>
-    <mergeCell ref="B204:B207"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="D51:D54"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="A104:A107"/>
-    <mergeCell ref="B132:B135"/>
-    <mergeCell ref="F156:F159"/>
-    <mergeCell ref="E160:E163"/>
-    <mergeCell ref="D188:D191"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="F188:F191"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="F35:F38"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="E43:E46"/>
-    <mergeCell ref="F84:F87"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="B116:B119"/>
-    <mergeCell ref="E196:E199"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="E180:E183"/>
-    <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A184:A187"/>
-    <mergeCell ref="D180:D183"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="B59:B71"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="C144:C147"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C124:C127"/>
-    <mergeCell ref="E31:E34"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="E124:E127"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="E80:E83"/>
-    <mergeCell ref="F112:F115"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B168:B171"/>
-    <mergeCell ref="E164:E167"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C92:C95"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="E200:E203"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="F124:F127"/>
-    <mergeCell ref="D164:D167"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="E132:E135"/>
-    <mergeCell ref="E88:E91"/>
-    <mergeCell ref="B180:B183"/>
-    <mergeCell ref="B196:B199"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="D152:D155"/>
-    <mergeCell ref="E184:E187"/>
-    <mergeCell ref="F31:F34"/>
-    <mergeCell ref="C172:C175"/>
-    <mergeCell ref="F47:F50"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="E51:E54"/>
-    <mergeCell ref="D92:D95"/>
-    <mergeCell ref="C96:C99"/>
-    <mergeCell ref="F92:F95"/>
-    <mergeCell ref="B208:B211"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="A116:A119"/>
-    <mergeCell ref="F15:F18"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B136:B139"/>
-    <mergeCell ref="D192:D195"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="F192:F195"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="B120:B123"/>
-    <mergeCell ref="E116:E119"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D120:D123"/>
-    <mergeCell ref="A59:A71"/>
-    <mergeCell ref="E156:E159"/>
-    <mergeCell ref="F176:F179"/>
-    <mergeCell ref="E208:E211"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="C136:C139"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="A96:A99"/>
-    <mergeCell ref="F148:F151"/>
-    <mergeCell ref="C152:C155"/>
-    <mergeCell ref="F100:F103"/>
-    <mergeCell ref="E128:E131"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="E47:E50"/>
-    <mergeCell ref="D76:D79"/>
-    <mergeCell ref="D116:D119"/>
-    <mergeCell ref="F76:F79"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="C148:C151"/>
-    <mergeCell ref="D31:D34"/>
-    <mergeCell ref="E55:E58"/>
-    <mergeCell ref="D72:D75"/>
-    <mergeCell ref="D128:D131"/>
-    <mergeCell ref="F72:F75"/>
-    <mergeCell ref="E136:E139"/>
-    <mergeCell ref="A144:A147"/>
-    <mergeCell ref="B172:B175"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="E144:E147"/>
-    <mergeCell ref="D148:D151"/>
-    <mergeCell ref="C168:C171"/>
-    <mergeCell ref="C128:C131"/>
-    <mergeCell ref="A168:A171"/>
-    <mergeCell ref="B156:B159"/>
-    <mergeCell ref="D156:D159"/>
-    <mergeCell ref="C59:C71"/>
-    <mergeCell ref="E59:E71"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="E148:E151"/>
-    <mergeCell ref="D168:D171"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="B144:B147"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="C204:C207"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D59:D71"/>
-    <mergeCell ref="F59:F71"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="C132:C135"/>
-    <mergeCell ref="C88:C91"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="C196:C199"/>
-    <mergeCell ref="D104:D107"/>
-    <mergeCell ref="E152:E155"/>
-    <mergeCell ref="E204:E207"/>
-    <mergeCell ref="B160:B163"/>
-    <mergeCell ref="A124:A127"/>
-    <mergeCell ref="A180:A183"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="F88:F91"/>
-    <mergeCell ref="C180:C183"/>
-    <mergeCell ref="F128:F131"/>
-    <mergeCell ref="F168:F171"/>
-    <mergeCell ref="B200:B203"/>
-    <mergeCell ref="D204:D207"/>
-    <mergeCell ref="A148:A151"/>
-    <mergeCell ref="F96:F99"/>
-    <mergeCell ref="F152:F155"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="E108:E111"/>
-    <mergeCell ref="F80:F83"/>
-    <mergeCell ref="E35:E38"/>
-    <mergeCell ref="D144:D147"/>
-    <mergeCell ref="F144:F147"/>
-    <mergeCell ref="E72:E75"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E96:E99"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="F51:F54"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="D140:D143"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C184:C187"/>
-    <mergeCell ref="F180:F183"/>
-    <mergeCell ref="B148:B151"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="D200:D203"/>
-    <mergeCell ref="F7:F10"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="E92:E95"/>
-    <mergeCell ref="D96:D99"/>
-    <mergeCell ref="B192:B195"/>
-    <mergeCell ref="B188:B191"/>
-    <mergeCell ref="E172:E175"/>
-    <mergeCell ref="F140:F143"/>
-    <mergeCell ref="F55:F58"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="F164:F167"/>
-    <mergeCell ref="D196:D199"/>
-    <mergeCell ref="E176:E179"/>
-    <mergeCell ref="F200:F203"/>
-    <mergeCell ref="C188:C191"/>
-    <mergeCell ref="E188:E191"/>
-    <mergeCell ref="F172:F175"/>
-    <mergeCell ref="C176:C179"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="A108:A111"/>
-    <mergeCell ref="F204:F207"/>
-    <mergeCell ref="A208:A211"/>
-    <mergeCell ref="C208:C211"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="D132:D135"/>
-    <mergeCell ref="F132:F135"/>
-    <mergeCell ref="A136:A139"/>
-    <mergeCell ref="C140:C143"/>
-    <mergeCell ref="D172:D175"/>
-    <mergeCell ref="C192:C195"/>
-    <mergeCell ref="A152:A155"/>
-    <mergeCell ref="E192:E195"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="F116:F119"/>
-    <mergeCell ref="F196:F199"/>
-    <mergeCell ref="C160:C163"/>
-    <mergeCell ref="A200:A203"/>
-    <mergeCell ref="C200:C203"/>
-    <mergeCell ref="B124:B127"/>
-    <mergeCell ref="D124:D127"/>
-    <mergeCell ref="B164:B167"/>
+    <mergeCell ref="F136:F139"/>
+    <mergeCell ref="D176:D179"/>
+    <mergeCell ref="E100:E103"/>
+    <mergeCell ref="F120:F123"/>
+    <mergeCell ref="D160:D163"/>
+    <mergeCell ref="F160:F163"/>
+    <mergeCell ref="E168:E171"/>
+    <mergeCell ref="B176:B179"/>
+    <mergeCell ref="B128:B131"/>
+    <mergeCell ref="F104:F107"/>
+    <mergeCell ref="E120:E123"/>
+    <mergeCell ref="F108:F111"/>
+    <mergeCell ref="E140:E143"/>
+    <mergeCell ref="A128:A131"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C108:C111"/>
+    <mergeCell ref="C164:C167"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="A176:A179"/>
+    <mergeCell ref="E112:E115"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="A172:A175"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="D208:D211"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="A156:A159"/>
+    <mergeCell ref="F208:F211"/>
+    <mergeCell ref="C156:C159"/>
+    <mergeCell ref="D184:D187"/>
+    <mergeCell ref="F184:F187"/>
+    <mergeCell ref="A188:A191"/>
+    <mergeCell ref="C104:C107"/>
+    <mergeCell ref="D136:D139"/>
+    <mergeCell ref="E104:E107"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FB9C12-4BA2-477E-BCD9-0BF15CB34D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E79CFD4-9A2F-4599-9DBE-7FCEC7EC9BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="209">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -56,15 +43,27 @@
     <t>Neg_001</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>ubat dan kohomada bn? Accident eken passe dakke ada ne itin.</t>
+  </si>
+  <si>
+    <t>උඹට දැන් කොහොමද බං? Accident එකෙන් පස්සේ දැක්කේ අද නෙ ඉතිං.</t>
+  </si>
+  <si>
+    <t>උඹට දැන් කොහොමද බන්? Accident එකෙන් පස්සේ දැක්කේ අද නෑ ඉතින්.</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Neg_002</t>
+  </si>
+  <si>
     <t>S</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>Neg_002</t>
-  </si>
-  <si>
     <t>oya enawada ada</t>
   </si>
   <si>
@@ -77,9 +76,6 @@
     <t>Neg_003</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>ubata theruna da mama kiyana de walin nathnam mama aye explain karannam</t>
   </si>
   <si>
@@ -122,6 +118,9 @@
     <t>අනේ බං මට මේ system එක use කරන්න අමාරුයි මොකද්ද මේ errors ටික එන්නේ</t>
   </si>
   <si>
+    <t>අනේ බන් මට මේ system එක use කරන්න අමාරුයි මොකද්ද මේ errors ටික එන්නේ</t>
+  </si>
+  <si>
     <t>Neg_007</t>
   </si>
   <si>
@@ -131,12 +130,33 @@
     <t>මම ඔයාට කිව්වා නේ මේක හරියට කරන්න කියලා ඒත් ඔයා එක ignore කළා</t>
   </si>
   <si>
+    <t>මම ඔයාට කිව්වා නේ මේක හරියට කරන්න කියලා ඒත් ඔය එක ඉඳුරෙ කරා</t>
+  </si>
+  <si>
     <t>Neg_008</t>
   </si>
   <si>
+    <t>Meka ikmant aran yanv metanin</t>
+  </si>
+  <si>
+    <t>මේක ඉක්මනට අරන් යනව මෙතනින්</t>
+  </si>
+  <si>
+    <t>මේක ඉක්මන්ට් අරන් යනවා මෙතනින්</t>
+  </si>
+  <si>
     <t>Neg_009</t>
   </si>
   <si>
+    <t>gaga lagad tiyenne</t>
+  </si>
+  <si>
+    <t>ගඟ ළඟද තියෙන්නේ</t>
+  </si>
+  <si>
+    <t>ගගා ලගඩ් තියෙන්නේ</t>
+  </si>
+  <si>
     <t>Neg_010</t>
   </si>
   <si>
@@ -158,6 +178,9 @@
     <t>ඔයාට කවද්ද එන්නේ?</t>
   </si>
   <si>
+    <t>ඔයාට කවද්ද එන්නේ???</t>
+  </si>
+  <si>
     <t>Neg_012</t>
   </si>
   <si>
@@ -167,6 +190,9 @@
     <t>ඔයා එනවද නැද්ද?</t>
   </si>
   <si>
+    <t>ඔයා එනවද නැද්ද??</t>
+  </si>
+  <si>
     <t>Neg_013</t>
   </si>
   <si>
@@ -176,9 +202,21 @@
     <t>මට කියන්න පුළුවන්ද මේක හරිද කියලා?</t>
   </si>
   <si>
+    <t>මට කියන්න පුලුවන්ද මේක හරි ද කියලා??</t>
+  </si>
+  <si>
     <t>Neg_014</t>
   </si>
   <si>
+    <t>mama kiwwa ennei kiyala habai awe ne</t>
+  </si>
+  <si>
+    <t>මම කිව්වා එන්නෙයි කියලා හැබැයි ආවෙ නැ</t>
+  </si>
+  <si>
+    <t>මම කිව්වා එන්නේයි කියලා හැබැයි ආවේ නෑ</t>
+  </si>
+  <si>
     <t>Neg_015</t>
   </si>
   <si>
@@ -188,6 +226,9 @@
     <t>"Ado machan, oya ara 2026-05-04th dhenna thiyena IT3040 assignment eka iwara kalada? Mata eeke Playwright automation scripts wala podi error ekak enawa. Puluwannm mata help ekak dhenna @Saman aiyee. Mama hithuwe Rs.1500k dila meka karaganna kiyala eth salli na ban. Me link eka balanna: https://github.com/sliit-student/repo-01. Eke thiyena README.md eka kiyewwama 100% sure wei wede hati. ASAP reply karapan hode!"</t>
   </si>
   <si>
+    <t>"අඩෝ මචං, ඔයා අර 2026-05-04ත දෙන්න තියෙන IT3040 assignment එක ඉවර කළාද? මට ඒකේ Playwright automation scripts වල පොඩි error එකක් එනවා. පුළුවන්නම් මට help එකක් දෙන්න @Saman අයියේ. මම හිතුවේ Rs.1500ක් දීලා මේක කරගන්න කියලා ඒත් සල්ලි නෑ බන්. මේ link එක බලන්න: https://github.com/sliit-student/repo-01. ඒකේ තියෙන README.md එක කියෙව්වම 100% sure වෙයි වැඩේ හැටි. ASAP reply කරපන් හොදේ!"</t>
+  </si>
+  <si>
     <t>Neg_016</t>
   </si>
   <si>
@@ -218,12 +259,24 @@
     <t>api yamu da nathnam inne da</t>
   </si>
   <si>
+    <t>අපි යමු ද නැත්නම් ඉන්නද</t>
+  </si>
+  <si>
     <t>අපි යමු ද නැත්නම් ඉන්නේ ද</t>
   </si>
   <si>
     <t>Neg_019</t>
   </si>
   <si>
+    <t>famasiye me pettiya 10kg barayi.</t>
+  </si>
+  <si>
+    <t>ෆාමසියෙ මේ පෙට්ටිය 10kg බරයි.</t>
+  </si>
+  <si>
+    <t>ෆාමසියේ මේ පෙට්ටිය 10kg බරයි.</t>
+  </si>
+  <si>
     <t>Neg_020</t>
   </si>
   <si>
@@ -251,6 +304,15 @@
     <t>Neg_022</t>
   </si>
   <si>
+    <t xml:space="preserve">mokadda ban me seen eka u pora kiyald hitan inne dan </t>
+  </si>
+  <si>
+    <t>මොකද්ද බං මේ සීන් එක ඌ පොර කියල ද හිතන් ඉන්නේ</t>
+  </si>
+  <si>
+    <t>මොකද්ද බන් මේ සීන් එක ඌ පොර කියලද හිටන් ඉන්නේ දැන්</t>
+  </si>
+  <si>
     <t>Neg_023</t>
   </si>
   <si>
@@ -269,6 +331,9 @@
     <t>ubat pissuda bn</t>
   </si>
   <si>
+    <t>උඹට පිස්සුද බං</t>
+  </si>
+  <si>
     <t>උඹට පිස්සුද බන්</t>
   </si>
   <si>
@@ -287,9 +352,6 @@
     <t>Neg_026</t>
   </si>
   <si>
-    <t>එළකිරි මචං</t>
-  </si>
-  <si>
     <t>Neg_027</t>
   </si>
   <si>
@@ -317,21 +379,51 @@
     <t>Neg_029</t>
   </si>
   <si>
+    <t>ohet password eka mathakei</t>
+  </si>
+  <si>
+    <t>ඔහේට password එක මතකෙයි</t>
+  </si>
+  <si>
+    <t>ඔහේට password එක මතකයි</t>
+  </si>
+  <si>
     <t>Neg_030</t>
   </si>
   <si>
     <t>oya thama SLIIT eke igena gannawada?</t>
   </si>
   <si>
+    <t>ඔයා තාම SLIIT එකේ ඉගෙන ගන්නවද?</t>
+  </si>
+  <si>
     <t>ඔයා තමා SLIIT ඒකෙ ඉගෙන ගන්නවද?</t>
   </si>
   <si>
     <t>Neg_031</t>
   </si>
   <si>
+    <t>oya courseweb.sliit.lk , web ekat giyad</t>
+  </si>
+  <si>
+    <t>ඔයා courseweb.sliit.lk , wed එකට ගියා ද</t>
+  </si>
+  <si>
+    <t>ඔය courseweb.ස්ලිට්.ල්ක් , වෙබ් එකට ගියාද</t>
+  </si>
+  <si>
     <t>Neg_032</t>
   </si>
   <si>
+    <t>youtube eke podi podi dewal balanna puluwan ne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">youtube එකේ පොඩි පොඩි දේවල් බලන්න පුළුවන් නේ </t>
+  </si>
+  <si>
+    <t>යූටූබ් එකේ පොඩි පොඩි දේවල් බලන්න පුළුවන් නේ</t>
+  </si>
+  <si>
     <t>Neg_033</t>
   </si>
   <si>
@@ -347,18 +439,39 @@
     <t>Neg_034</t>
   </si>
   <si>
-    <t>ඔබට සුබ දවසක් ප්‍රාර්ථනා කරනවා!</t>
+    <t>Obata suba dhavasak prarthana karanawa!😊</t>
+  </si>
+  <si>
+    <t>ඔබට සුභ දවසක් ප්‍රාර්ථනා කරනවා!</t>
+  </si>
+  <si>
+    <t>ඔබට සුබ දවසක් ප්‍රාර්ථනා කරනවා!😊</t>
   </si>
   <si>
     <t>Neg_035</t>
   </si>
   <si>
+    <t>lamai oyalat subha rathriyak wewa!</t>
+  </si>
+  <si>
+    <t>ළමයි ඔයාලට සුභ රාත්‍රියක් වේවා!</t>
+  </si>
+  <si>
+    <t>ළමයි ඔයාලත් සුභ රාත්‍රියක් වේවා!</t>
+  </si>
+  <si>
     <t>Neg_036</t>
   </si>
   <si>
+    <t>bus eka 10.30 ta env</t>
+  </si>
+  <si>
     <t>bus එක 10.30 ට එනවා</t>
   </si>
   <si>
+    <t>bus එක 10.30 ට එන්ව්</t>
+  </si>
+  <si>
     <t>Neg_037</t>
   </si>
   <si>
@@ -377,6 +490,12 @@
     <t>oyage bdy eka kawadda?</t>
   </si>
   <si>
+    <t>ඔයාගේ birthday එක කවද්ද?</t>
+  </si>
+  <si>
+    <t>ඔයාගෙ bdy එක කවද්ද?</t>
+  </si>
+  <si>
     <t>Neg_039</t>
   </si>
   <si>
@@ -416,6 +535,15 @@
     <t>Neg_042</t>
   </si>
   <si>
+    <t>class eka 8.00am patan gannav.oyala 15 min tiyala class eka lagat enna hode.</t>
+  </si>
+  <si>
+    <t>class එක 8.00am පටන් ගන්නවා. ඔයාලා 5 min තියලා  එක ලඟට එන්න හොඳේ.</t>
+  </si>
+  <si>
+    <t>class එක 8.00am පටන් ගන්නවා.ඔයාලා 15 මින් තියලා class එක ලගට් එන්න හොදේ.</t>
+  </si>
+  <si>
     <t>Neg_043</t>
   </si>
   <si>
@@ -443,6 +571,15 @@
     <t>Neg_045</t>
   </si>
   <si>
+    <t>Ado @saman , machan mama kiwwa ne enne kiyala eth oya awilla ne 😡 eka nisa mama upset</t>
+  </si>
+  <si>
+    <t>අඩෝ @සමන් , මචං මම කිව්වා නේ එන්නේ කියලා ඒත් ඔයා ඇවිල්ලා නෑ 😡 ඒක නිසා මම upset</t>
+  </si>
+  <si>
+    <t>අඩෝ @සමන් , මචං මම කිව්වා නේ එන්නේ කියලා ඒත් ඔයා ඇවිල්ලා නෑ 🤣 ඒක නිසා මම upset</t>
+  </si>
+  <si>
     <t>Neg_046</t>
   </si>
   <si>
@@ -452,224 +589,71 @@
     <t>අනේ බං මේක හරියට වැඩක් නෑ system එක හරියට වැඩ කරන්නේ නැ</t>
   </si>
   <si>
+    <t>අනේ බන් මේක හරියට වැඩක් නෑ system එක හරියට වැඩ කරන්නේ නැ</t>
+  </si>
+  <si>
     <t>Neg_047</t>
   </si>
   <si>
+    <t>mama oyata call karanna try kala eth oya phone eka answer kale ne</t>
+  </si>
+  <si>
     <t>මම ඔයාට call කරන්න try කළා ඒත් ඔයා phone එක answer කළේ නැ</t>
   </si>
   <si>
+    <t>මම ඔයාට call කරන්න try කලා එත් ඔයා phone එක answer කලේ නෑ</t>
+  </si>
+  <si>
     <t>Neg_048</t>
   </si>
   <si>
+    <t>oyat amba gediyak kadala denna puluwan athi kiyala api sakachcha una. Oyat pulawand itin. Ane api santhoshai oyat puluwan nam, nattam aparade prayoganayak natuv yanv gedi tika.balannako poddak</t>
+  </si>
+  <si>
+    <t>ඔයාට අඔ ගෙඩියක් කඩලා දෙන්න පුළුයන් ඇති කියලා අපි සාකච්චා උනා.ඔයාට පුළුවන්ද ඉතින්. අනේ අපි සන්තෝෂයි ඔයාට පුළුවන් නම්, නැත්නම් අපරාදේ ප්‍රයෝජනයක් නැතුව යනව ගෙඩි ටික.බලන්නකෝ පොඩ්ඩක්.</t>
+  </si>
+  <si>
+    <t>ඔයාට අඹ ගෙඩියක් කඩලා දෙන්න පුළුවන් ඇති කියලා අපි සාකච්ඡා උනා. ඔයාට පුලුවන්ද ඉතින්. අනේ අපි සන්තෝෂයි ඔයාට පුළුවන් නම්, නැත්නම් අපරාදේ ප්රයෝගනයක් නැතුව යනවාගෙඩි ටික.බලන්නකෝ පොඩ්ඩක්</t>
+  </si>
+  <si>
     <t>Neg_049</t>
   </si>
   <si>
     <t>uba danne nadda bn mama oyata kiyapu dewal tika mama aye aye kiyanna one ne mama ekama deyak kiyala thiyenne hariyata wada karanna kiyala eth oya eka ignore karanawa wage penawa mata nam pissu yanne mehema giyoth api project eka complete karanna kalinma deadline eka pass wenawa 😅</t>
   </si>
   <si>
+    <t>උඹ දන්නේ නැද්ද බං මම ඔයාට කියපු දේවල් ටික මම ආයෙ ආයෙ කියන්න ඕනේ නෑ මම එකම දෙයක් කියලා තියෙන්නේ හරියට වැඩ කරන්න කියලා ඒත් ඔයා එක ignore කරනවා වගේ පේනවා මට නම් පිස්සු යන්නේ මෙහෙම ගියොත් අපි project එක complete කරන්න කලින්ම deadline එක පාස් වෙනවා 😅</t>
+  </si>
+  <si>
+    <t>උබ දන්නේ නැද්ද බන් මම ඔයාට කියපු දේවල් ටික මම ආයෙ ආයෙ කියන්න ඔන‍ෙ නැ මම එකම දෙයක් කියලා තියෙන්නේ හරියට වැඩ කරන්න කියලා ඒත් ඔයා එක ignore කරනවා වගේ පේනවා මට නම් පිස්සු යන්නේ මෙහෙම ගියොත් අපි project එක complete කරන්න කලින්ම deadline එක පස් වෙනවා 😅</t>
+  </si>
+  <si>
     <t>Neg_050</t>
   </si>
   <si>
-    <t>lamai oyalat subha rathriyak wewa!</t>
-  </si>
-  <si>
-    <t>ළමයි ඔයාලට සුභ රාත්‍රියක් වේවා!</t>
-  </si>
-  <si>
-    <t>Obata suba dhavasak prarthana karanawa!😊</t>
-  </si>
-  <si>
-    <t>අනේ බන් මේක හරියට වැඩක් නෑ system එක හරියට වැඩ කරන්නේ නැ</t>
-  </si>
-  <si>
-    <t>මම ඔයාට call කරන්න try කලා එත් ඔයා phone එක answer කලේ නෑ</t>
-  </si>
-  <si>
-    <t>mama oyata call karanna try kala eth oya phone eka answer kale ne</t>
-  </si>
-  <si>
-    <t>උඹ දන්නේ නැද්ද බං මම ඔයාට කියපු දේවල් ටික මම ආයෙ ආයෙ කියන්න ඕනේ නෑ මම එකම දෙයක් කියලා තියෙන්නේ හරියට වැඩ කරන්න කියලා ඒත් ඔයා එක ignore කරනවා වගේ පේනවා මට නම් පිස්සු යන්නේ මෙහෙම ගියොත් අපි project එක complete කරන්න කලින්ම deadline එක පාස් වෙනවා 😅</t>
-  </si>
-  <si>
-    <t>උබ දන්නේ නැද්ද බන් මම ඔයාට කියපු දේවල් ටික මම ආයෙ ආයෙ කියන්න ඔන‍ෙ නැ මම එකම දෙයක් කියලා තියෙන්නේ හරියට වැඩ කරන්න කියලා ඒත් ඔයා එක ignore කරනවා වගේ පේනවා මට නම් පිස්සු යන්නේ මෙහෙම ගියොත් අපි project එක complete කරන්න කලින්ම deadline එක පස් වෙනවා 😅</t>
-  </si>
-  <si>
-    <t>class eka 8.00am patan gannav.oyala 15 min tiyala class eka lagat enna hode.</t>
-  </si>
-  <si>
-    <t>class එක 8.00am පටන් ගන්නවා.ඔයාලා 15 මින් තියලා class එක ලගට් එන්න හොදේ.</t>
-  </si>
-  <si>
-    <t>class එක 8.00am පටන් ගන්නවා. ඔයාලා 5 min තියලා  එක ලඟට එන්න හොඳේ.</t>
-  </si>
-  <si>
-    <t>ඔයාගෙ bdy එක කවද්ද?</t>
-  </si>
-  <si>
-    <t>ඔයාගේ birthday එක කවද්ද?</t>
-  </si>
-  <si>
-    <t>bus eka 10.30 ta env</t>
-  </si>
-  <si>
-    <t>bus එක 10.30 ට එන්ව්</t>
-  </si>
-  <si>
-    <t>ළමයි ඔයාලත් සුභ රාත්‍රියක් වේවා!</t>
-  </si>
-  <si>
-    <t>ඔබට සුභ දවසක් ප්‍රාර්ථනා කරනවා!</t>
-  </si>
-  <si>
-    <t>ඔයා තාම SLIIT එකේ ඉගෙන ගන්නවද?</t>
-  </si>
-  <si>
-    <t>ohet password eka mathakei</t>
-  </si>
-  <si>
-    <t>ඔහේට password එක මතකෙයි</t>
-  </si>
-  <si>
-    <t>ඔහේට password එක මතකයි</t>
-  </si>
-  <si>
-    <t>elakiri machan</t>
-  </si>
-  <si>
-    <t>එලකිරි මචං</t>
-  </si>
-  <si>
-    <t>උඹට පිස්සුද බං</t>
-  </si>
-  <si>
-    <t>මොකද්ද බං මේ සීන් එක ඌ පොර කියල ද හිතන් ඉන්නේ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mokadda ban me seen eka u pora kiyald hitan inne dan </t>
-  </si>
-  <si>
-    <t>මොකද්ද බන් මේ සීන් එක ඌ පොර කියලද හිටන් ඉන්නේ දැන්</t>
-  </si>
-  <si>
-    <t>ෆාමසියෙ මේ පෙට්ටිය 10kg බරයි.</t>
-  </si>
-  <si>
-    <t>famasiye me pettiya 10kg barayi.</t>
-  </si>
-  <si>
-    <t>ෆාමසියේ මේ පෙට්ටිය 10kg බරයි..</t>
-  </si>
-  <si>
-    <t>අපි යමු ද නැත්නම් ඉන්නද</t>
-  </si>
-  <si>
-    <t>අඩෝ මචන්, ඔයා අර 2026-05-04ත් දෙන්න තියෙන IT3040 assignment එක ඉවර කළාද? මට ඒකේ Playwright automation scripts වල පොඩි error එකක් එනවා. පුලුවන්නම් මට help එකක් දෙන්න @සමන් අයියේ. මම හිතුවේ Rs.1500ක් දිලා මේක කරගන්න කියලා ඒත් සල්ලි නෑ බං. මේ link එක බලන්න: https://github.com/sliit-student/repo-01ඒකේ තියෙන README.ම්ද් එක කියෙව්වම 100% sure වෙයි වැඩේ හැටි. ASAP reply කරපන් හොඳේ!"</t>
-  </si>
-  <si>
-    <t>mama kiwwa ennei kiyala habai awe ne</t>
-  </si>
-  <si>
-    <t>මම කිව්වා එන්නේයි කියලා හැබැයි ආවේ නෑ</t>
-  </si>
-  <si>
-    <t>මට කියන්න පුලුවන්ද මේක හරි ද කියලා??</t>
-  </si>
-  <si>
-    <t>ඔයා එනවද නැද්ද??</t>
-  </si>
-  <si>
-    <t>ඔයාට කවද්ද එන්නේ???</t>
-  </si>
-  <si>
-    <t>Meka ikmant aran yanv metanin</t>
-  </si>
-  <si>
-    <t>මේක ඉක්මනට අරන් යනව මෙතනින්</t>
-  </si>
-  <si>
-    <t>මේක ඉක්මන්ට් අරන් යනවා මෙතනින්</t>
-  </si>
-  <si>
-    <t>මම ඔයාට කිව්වා නේ මේක හරියට කරන්න කියලා ඒත් ඔය එක ඉඳුරෙ කරා</t>
-  </si>
-  <si>
-    <t>අනේ බන් මට මේ system එක use කරන්න අමාරුයි මොකද්ද මේ errors ටික එන්නේ</t>
-  </si>
-  <si>
-    <t>උඹට දැන් කොහොමද බං? Accident එකෙන් පස්සේ දැක්කේ අද නෙ ඉතිං.</t>
-  </si>
-  <si>
-    <t>ubat dan kohomada bn? Accident eken passe dakke ada ne itin.</t>
-  </si>
-  <si>
-    <t>උඹට දැන් කොහොමද බන්? Accident එකෙන් පස්සේ දැක්කේ අද නෑ ඉතින්.</t>
-  </si>
-  <si>
-    <t>gaga lagad tiyenne</t>
-  </si>
-  <si>
-    <t>ගඟ ළඟද තියෙන්නේ</t>
-  </si>
-  <si>
-    <t>ගගා ලගඩ් තියෙන්නේ</t>
-  </si>
-  <si>
-    <t>oya courseweb.sliit.lk , web ekat giyad</t>
-  </si>
-  <si>
-    <t>ඔයා courseweb.sliit.lk , wed එකට ගියා ද</t>
-  </si>
-  <si>
-    <t>ඔය courseweb.ස්ලිට්.ල්ක් , වෙබ් එකට ගියාද</t>
-  </si>
-  <si>
-    <t>youtube eke podi podi dewal balanna puluwan ne</t>
-  </si>
-  <si>
-    <t>යූටූබ් එකේ පොඩි පොඩි දේවල් බලන්න පුළුවන් නේ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">youtube එකේ පොඩි පොඩි දේවල් බලන්න පුළුවන් නේ </t>
-  </si>
-  <si>
-    <t>Ado @saman , machan mama kiwwa ne enne kiyala eth oya awilla ne 😡 eka nisa mama upset</t>
-  </si>
-  <si>
-    <t>අඩෝ @සමන් , මචං මම කිව්වා නේ එන්නේ කියලා ඒත් ඔයා ඇවිල්ලා නෑ 🤣 ඒක නිසා මම upset</t>
-  </si>
-  <si>
-    <t>අඩෝ @සමන් , මචං මම කිව්වා නේ එන්නේ කියලා ඒත් ඔයා ඇවිල්ලා නෑ 😡 ඒක නිසා මම upset</t>
-  </si>
-  <si>
     <t>fathima , london walat shita rituv labalad dan?</t>
   </si>
   <si>
+    <t>ෆාතිමා , ලන්ඩන් වලට ශීත ඍතුව ලබලාද දැන්?</t>
+  </si>
+  <si>
     <t>fathima , london වලට ෂිටා රිටිව් ලාබාලඩ් දාන්?</t>
   </si>
   <si>
-    <t>ෆාතිමා , ලන්ඩන් වලට ශීත ඍතුව ලබලාද දැන්?</t>
-  </si>
-  <si>
-    <t>ඔයාට අඹ ගෙඩියක් කඩලා දෙන්න පුළුවන් ඇති කියලා අපි සාකච්ඡා උනා. ඔයාට පුලුවන්ද ඉතින්. අනේ අපි සන්තෝෂයි ඔයාට පුළුවන් නම්, නැත්නම් අපරාදේ ප්රයෝගනයක් නැතුව යනවාගෙඩි ටික.බලන්නකෝ පොඩ්ඩක්</t>
-  </si>
-  <si>
-    <t>oyat amba gediyak kadala denna puluwan athi kiyala api sakachcha una. Oyat pulawand itin. Ane api santhoshai oyat puluwan nam, nattam aparade prayoganayak natuv yanv gedi tika.balannako poddak</t>
-  </si>
-  <si>
-    <t>ඔයාට අඔ ගෙඩියක් කඩලා දෙන්න පුළුයන් ඇති කියලා අපි සාකච්චා උනා.ඔයාට පුළුවන්ද ඉතින්. අනේ අපි සන්තෝෂයි ඔයාට පුළුවන් නම්, නැත්නම් අපරාදේ ප්‍රයෝජනයක් නැතුව යනව ගෙඩි ටික.බලන්නකෝ පොඩ්ඩක්.</t>
-  </si>
-  <si>
-    <t>"අඩෝ මචං, ඔයා අර 2026-05-04ත දෙන්න තියෙන IT3040 assignment එක ඉවර කළාද? මට ඒකේ Playwright automation scripts වල පොඩි error එකක් එනවා. පුළුවන්නම් මට help එකක් දෙන්න @Saman අයියේ. මම හිතුවේ Rs.1500ක් දීලා මේක කරගන්න කියලා ඒත් සල්ලි නෑ බන්. මේ link එක බලන්න: https://github.com/sliit-student/repo-01. ඒකේ තියෙන README.md එක කියෙව්වම 100% sure වෙයි වැඩේ හැටි. ASAP reply කරපන් හොදේ!"</t>
-  </si>
-  <si>
-    <t>මම කිව්වා එන්නෙයි කියලා හැබැයි ආවෙ නැ</t>
+    <t xml:space="preserve"> ade ayye elakiri machan</t>
+  </si>
+  <si>
+    <t>අඩේ අය්යේ එළකිරි මචං</t>
+  </si>
+  <si>
+    <t>අඩේ අයියේ එළකිරි මචං</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,12 +711,6 @@
       <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -827,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -841,55 +819,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -899,7 +856,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1212,23 +1171,23 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" s="17" t="s">
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>8</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1236,7 +1195,7 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="27"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1244,7 +1203,7 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="27"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1252,7 +1211,7 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="27"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1260,27 +1219,27 @@
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="28"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>8</v>
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1289,7 +1248,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="29"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
@@ -1297,7 +1256,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
@@ -1305,26 +1264,26 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="29"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="13" t="s">
+      <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>8</v>
+      <c r="B11" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1352,23 +1311,23 @@
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>8</v>
+      <c r="B15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1396,28 +1355,28 @@
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>8</v>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
-      <c r="B20" s="14"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -1425,7 +1384,7 @@
     </row>
     <row r="21" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
-      <c r="B21" s="14"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -1433,35 +1392,35 @@
     </row>
     <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
-      <c r="B22" s="15"/>
+      <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>8</v>
+      <c r="A23" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
-      <c r="B24" s="14"/>
+      <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -1469,7 +1428,7 @@
     </row>
     <row r="25" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
-      <c r="B25" s="14"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -1477,35 +1436,35 @@
     </row>
     <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
-      <c r="B26" s="15"/>
+      <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>8</v>
+      <c r="A27" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
-      <c r="B28" s="18"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -1513,7 +1472,7 @@
     </row>
     <row r="29" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
-      <c r="B29" s="18"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -1521,35 +1480,35 @@
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
-      <c r="B30" s="19"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>8</v>
+      <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
-      <c r="B32" s="14"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -1557,7 +1516,7 @@
     </row>
     <row r="33" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
-      <c r="B33" s="14"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -1565,35 +1524,35 @@
     </row>
     <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
-      <c r="B34" s="15"/>
+      <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>8</v>
+      <c r="A35" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
-      <c r="B36" s="14"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -1601,7 +1560,7 @@
     </row>
     <row r="37" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
-      <c r="B37" s="14"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -1609,30 +1568,30 @@
     </row>
     <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="B38" s="15"/>
+      <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
     <row r="39" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>8</v>
+      <c r="A39" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1660,23 +1619,23 @@
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>8</v>
+      <c r="A43" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1704,23 +1663,23 @@
       <c r="F46" s="9"/>
     </row>
     <row r="47" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>8</v>
+      <c r="A47" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1748,28 +1707,28 @@
       <c r="F50" s="9"/>
     </row>
     <row r="51" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>8</v>
+      <c r="A51" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
-      <c r="B52" s="14"/>
+      <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
@@ -1777,7 +1736,7 @@
     </row>
     <row r="53" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
-      <c r="B53" s="14"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
@@ -1785,30 +1744,30 @@
     </row>
     <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
-      <c r="B54" s="15"/>
+      <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
     <row r="55" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>8</v>
+      <c r="A55" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1836,23 +1795,21 @@
       <c r="F58" s="9"/>
     </row>
     <row r="59" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>8</v>
+      <c r="A59" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="10"/>
+      <c r="F59" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1952,28 +1909,28 @@
       <c r="F71" s="9"/>
     </row>
     <row r="72" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>8</v>
+      <c r="A72" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
-      <c r="B73" s="14"/>
+      <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
@@ -1981,7 +1938,7 @@
     </row>
     <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
-      <c r="B74" s="14"/>
+      <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
@@ -1989,30 +1946,30 @@
     </row>
     <row r="75" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
-      <c r="B75" s="15"/>
+      <c r="B75" s="9"/>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
     </row>
     <row r="76" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>8</v>
+      <c r="A76" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2040,23 +1997,23 @@
       <c r="F79" s="9"/>
     </row>
     <row r="80" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F80" s="17" t="s">
-        <v>8</v>
+      <c r="A80" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2084,23 +2041,23 @@
       <c r="F83" s="9"/>
     </row>
     <row r="84" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F84" s="17" t="s">
-        <v>8</v>
+      <c r="A84" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F84" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2128,23 +2085,23 @@
       <c r="F87" s="9"/>
     </row>
     <row r="88" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B88" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F88" s="17" t="s">
-        <v>8</v>
+      <c r="A88" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2172,23 +2129,23 @@
       <c r="F91" s="9"/>
     </row>
     <row r="92" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F92" s="17" t="s">
-        <v>8</v>
+      <c r="A92" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F92" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2216,67 +2173,67 @@
       <c r="F95" s="9"/>
     </row>
     <row r="96" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B96" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F96" s="17" t="s">
-        <v>8</v>
+      <c r="A96" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F96" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
     </row>
     <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="23"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
     <row r="99" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="24"/>
-      <c r="D99" s="24"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
     </row>
     <row r="100" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B100" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F100" s="17" t="s">
-        <v>8</v>
+      <c r="A100" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2304,23 +2261,23 @@
       <c r="F103" s="9"/>
     </row>
     <row r="104" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B104" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D104" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F104" s="17" t="s">
-        <v>8</v>
+      <c r="A104" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2348,23 +2305,23 @@
       <c r="F107" s="9"/>
     </row>
     <row r="108" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B108" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D108" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E108" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F108" s="17" t="s">
-        <v>8</v>
+      <c r="A108" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2392,23 +2349,23 @@
       <c r="F111" s="9"/>
     </row>
     <row r="112" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D112" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F112" s="17" t="s">
-        <v>8</v>
+      <c r="A112" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F112" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2436,23 +2393,23 @@
       <c r="F115" s="9"/>
     </row>
     <row r="116" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D116" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F116" s="17" t="s">
-        <v>8</v>
+      <c r="A116" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F116" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2480,23 +2437,23 @@
       <c r="F119" s="9"/>
     </row>
     <row r="120" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F120" s="17" t="s">
-        <v>8</v>
+      <c r="A120" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2524,23 +2481,23 @@
       <c r="F123" s="9"/>
     </row>
     <row r="124" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B124" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D124" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F124" s="17" t="s">
-        <v>8</v>
+      <c r="A124" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2568,23 +2525,23 @@
       <c r="F127" s="9"/>
     </row>
     <row r="128" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D128" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F128" s="17" t="s">
-        <v>8</v>
+      <c r="A128" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2612,23 +2569,23 @@
       <c r="F131" s="9"/>
     </row>
     <row r="132" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B132" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D132" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F132" s="17" t="s">
-        <v>8</v>
+      <c r="A132" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2656,23 +2613,23 @@
       <c r="F135" s="9"/>
     </row>
     <row r="136" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>8</v>
+      <c r="A136" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2700,23 +2657,23 @@
       <c r="F139" s="9"/>
     </row>
     <row r="140" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B140" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D140" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E140" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>8</v>
+      <c r="A140" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F140" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2744,29 +2701,29 @@
       <c r="F143" s="9"/>
     </row>
     <row r="144" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B144" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D144" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F144" s="17" t="s">
-        <v>8</v>
+      <c r="A144" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F144" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
-      <c r="C145" s="23"/>
+      <c r="C145" s="8"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
@@ -2774,7 +2731,7 @@
     <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
-      <c r="C146" s="23"/>
+      <c r="C146" s="8"/>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
@@ -2782,35 +2739,35 @@
     <row r="147" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
-      <c r="C147" s="24"/>
+      <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
     </row>
     <row r="148" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B148" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="11" t="s">
+      <c r="A148" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E148" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D148" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E148" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="F148" s="17" t="s">
-        <v>8</v>
+      <c r="F148" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
-      <c r="C149" s="23"/>
+      <c r="C149" s="8"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
@@ -2818,7 +2775,7 @@
     <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
-      <c r="C150" s="23"/>
+      <c r="C150" s="8"/>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
@@ -2826,29 +2783,29 @@
     <row r="151" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
-      <c r="C151" s="24"/>
+      <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
     </row>
     <row r="152" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B152" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D152" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E152" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F152" s="17" t="s">
-        <v>8</v>
+      <c r="A152" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F152" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2876,23 +2833,23 @@
       <c r="F155" s="9"/>
     </row>
     <row r="156" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C156" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D156" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E156" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F156" s="17" t="s">
-        <v>8</v>
+      <c r="A156" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F156" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2920,23 +2877,23 @@
       <c r="F159" s="9"/>
     </row>
     <row r="160" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B160" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D160" s="16" t="s">
+      <c r="A160" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D160" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E160" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E160" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F160" s="17" t="s">
-        <v>8</v>
+      <c r="F160" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2964,23 +2921,23 @@
       <c r="F163" s="9"/>
     </row>
     <row r="164" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B164" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D164" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E164" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F164" s="17" t="s">
-        <v>8</v>
+      <c r="A164" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F164" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3008,23 +2965,23 @@
       <c r="F167" s="9"/>
     </row>
     <row r="168" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B168" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D168" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E168" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F168" s="17" t="s">
-        <v>8</v>
+      <c r="A168" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E168" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F168" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3052,23 +3009,23 @@
       <c r="F171" s="9"/>
     </row>
     <row r="172" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D172" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E172" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="F172" s="17" t="s">
-        <v>8</v>
+      <c r="A172" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F172" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3096,23 +3053,23 @@
       <c r="F175" s="9"/>
     </row>
     <row r="176" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B176" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C176" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D176" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E176" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F176" s="17" t="s">
-        <v>8</v>
+      <c r="A176" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D176" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F176" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3140,23 +3097,23 @@
       <c r="F179" s="9"/>
     </row>
     <row r="180" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B180" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C180" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D180" s="20" t="s">
-        <v>129</v>
+      <c r="A180" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="E180" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="F180" s="17" t="s">
-        <v>8</v>
+        <v>177</v>
+      </c>
+      <c r="F180" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3184,23 +3141,23 @@
       <c r="F183" s="9"/>
     </row>
     <row r="184" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B184" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C184" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D184" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="E184" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F184" s="17" t="s">
-        <v>8</v>
+      <c r="A184" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D184" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F184" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3228,23 +3185,23 @@
       <c r="F187" s="9"/>
     </row>
     <row r="188" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C188" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D188" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="E188" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F188" s="17" t="s">
-        <v>8</v>
+      <c r="A188" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3272,23 +3229,23 @@
       <c r="F191" s="9"/>
     </row>
     <row r="192" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C192" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D192" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F192" s="17" t="s">
-        <v>8</v>
+      <c r="A192" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D192" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F192" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3316,23 +3273,23 @@
       <c r="F195" s="9"/>
     </row>
     <row r="196" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B196" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C196" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D196" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E196" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="F196" s="17" t="s">
-        <v>8</v>
+      <c r="A196" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D196" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F196" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3360,23 +3317,23 @@
       <c r="F199" s="9"/>
     </row>
     <row r="200" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B200" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C200" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D200" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E200" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="F200" s="17" t="s">
-        <v>8</v>
+      <c r="A200" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D200" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F200" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3404,23 +3361,23 @@
       <c r="F203" s="9"/>
     </row>
     <row r="204" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C204" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D204" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E204" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="F204" s="17" t="s">
-        <v>8</v>
+      <c r="A204" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D204" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F204" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3448,23 +3405,23 @@
       <c r="F207" s="9"/>
     </row>
     <row r="208" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B208" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C208" s="11" t="s">
+      <c r="A208" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D208" s="16" t="s">
+      <c r="B208" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D208" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="E208" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F208" s="17" t="s">
-        <v>8</v>
+      <c r="E208" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F208" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3493,308 +3450,307 @@
     </row>
   </sheetData>
   <mergeCells count="300">
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="A112:A115"/>
+    <mergeCell ref="D176:D179"/>
+    <mergeCell ref="A180:A183"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="D148:D151"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="A152:A155"/>
+    <mergeCell ref="F148:F151"/>
+    <mergeCell ref="E116:E119"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B160:B163"/>
+    <mergeCell ref="E72:E75"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="E168:E171"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="D19:D22"/>
+    <mergeCell ref="B59:B71"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="F172:F175"/>
+    <mergeCell ref="F200:F203"/>
+    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="B128:B131"/>
+    <mergeCell ref="A188:A191"/>
+    <mergeCell ref="D184:D187"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="C188:C191"/>
+    <mergeCell ref="F184:F187"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="B168:B171"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D168:D171"/>
+    <mergeCell ref="A116:A119"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="F120:F123"/>
+    <mergeCell ref="D164:D167"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="D188:D191"/>
+    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="A176:A179"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="A148:A151"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="F84:F87"/>
+    <mergeCell ref="C184:C187"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="D108:D111"/>
+    <mergeCell ref="B152:B155"/>
+    <mergeCell ref="F15:F18"/>
+    <mergeCell ref="D80:D83"/>
+    <mergeCell ref="F108:F111"/>
+    <mergeCell ref="A172:A175"/>
+    <mergeCell ref="F80:F83"/>
+    <mergeCell ref="B180:B183"/>
+    <mergeCell ref="C172:C175"/>
+    <mergeCell ref="B136:B139"/>
+    <mergeCell ref="C104:C107"/>
+    <mergeCell ref="C208:C211"/>
+    <mergeCell ref="E208:E211"/>
+    <mergeCell ref="A184:A187"/>
+    <mergeCell ref="E100:E103"/>
+    <mergeCell ref="D132:D135"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="F92:F95"/>
+    <mergeCell ref="F132:F135"/>
+    <mergeCell ref="B164:B167"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="E192:E195"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="E96:E99"/>
+    <mergeCell ref="B204:B207"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="F116:F119"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="D208:D211"/>
+    <mergeCell ref="F208:F211"/>
+    <mergeCell ref="D136:D139"/>
+    <mergeCell ref="C156:C159"/>
+    <mergeCell ref="F192:F195"/>
+    <mergeCell ref="F156:F159"/>
+    <mergeCell ref="F51:F54"/>
+    <mergeCell ref="A136:A139"/>
+    <mergeCell ref="F140:F143"/>
+    <mergeCell ref="E108:E111"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="A144:A147"/>
+    <mergeCell ref="C144:C147"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="E51:E54"/>
+    <mergeCell ref="F144:F147"/>
+    <mergeCell ref="C59:C71"/>
+    <mergeCell ref="E59:E71"/>
+    <mergeCell ref="A124:A127"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="C124:C127"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="F168:F171"/>
+    <mergeCell ref="F112:F115"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A196:A199"/>
+    <mergeCell ref="C196:C199"/>
+    <mergeCell ref="E19:E22"/>
+    <mergeCell ref="E132:E135"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="C180:C183"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="E180:E183"/>
+    <mergeCell ref="C152:C155"/>
+    <mergeCell ref="E152:E155"/>
+    <mergeCell ref="D104:D107"/>
+    <mergeCell ref="B88:B91"/>
+    <mergeCell ref="D160:D163"/>
+    <mergeCell ref="A108:A111"/>
+    <mergeCell ref="F160:F163"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="F104:F107"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="F76:F79"/>
+    <mergeCell ref="C204:C207"/>
+    <mergeCell ref="E204:E207"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="A132:A135"/>
+    <mergeCell ref="E188:E191"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="C80:C83"/>
+    <mergeCell ref="B176:B179"/>
+    <mergeCell ref="A200:A203"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="D200:D203"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="F204:F207"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="C192:C195"/>
+    <mergeCell ref="F100:F103"/>
+    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="C164:C167"/>
+    <mergeCell ref="B172:B175"/>
+    <mergeCell ref="E80:E83"/>
+    <mergeCell ref="F35:F38"/>
+    <mergeCell ref="C176:C179"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="E148:E151"/>
+    <mergeCell ref="D156:D159"/>
+    <mergeCell ref="B196:B199"/>
+    <mergeCell ref="A104:A107"/>
+    <mergeCell ref="A160:A163"/>
+    <mergeCell ref="D196:D199"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="D92:D95"/>
+    <mergeCell ref="C120:C123"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="D59:D71"/>
+    <mergeCell ref="C200:C203"/>
+    <mergeCell ref="E200:E203"/>
+    <mergeCell ref="B120:B123"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="D120:D123"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="A128:A131"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="C128:C131"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="E84:E87"/>
+    <mergeCell ref="B148:B151"/>
+    <mergeCell ref="E31:E34"/>
+    <mergeCell ref="E176:E179"/>
+    <mergeCell ref="A168:A171"/>
+    <mergeCell ref="C112:C115"/>
+    <mergeCell ref="C168:C171"/>
     <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="A108:A111"/>
-    <mergeCell ref="F204:F207"/>
-    <mergeCell ref="A208:A211"/>
-    <mergeCell ref="C208:C211"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="D132:D135"/>
-    <mergeCell ref="F132:F135"/>
-    <mergeCell ref="A136:A139"/>
-    <mergeCell ref="C140:C143"/>
-    <mergeCell ref="D172:D175"/>
-    <mergeCell ref="C192:C195"/>
-    <mergeCell ref="A152:A155"/>
-    <mergeCell ref="E192:E195"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="F116:F119"/>
-    <mergeCell ref="F196:F199"/>
-    <mergeCell ref="C160:C163"/>
-    <mergeCell ref="A200:A203"/>
-    <mergeCell ref="C200:C203"/>
     <mergeCell ref="B124:B127"/>
-    <mergeCell ref="D124:D127"/>
-    <mergeCell ref="B164:B167"/>
-    <mergeCell ref="C184:C187"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="E120:E123"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B200:B203"/>
+    <mergeCell ref="F176:F179"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="D128:D131"/>
+    <mergeCell ref="F128:F131"/>
+    <mergeCell ref="E160:E163"/>
+    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="C136:C139"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="E136:E139"/>
+    <mergeCell ref="D51:D54"/>
+    <mergeCell ref="E92:E95"/>
+    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="F164:F167"/>
+    <mergeCell ref="A156:A159"/>
+    <mergeCell ref="E172:E175"/>
+    <mergeCell ref="D180:D183"/>
     <mergeCell ref="F180:F183"/>
-    <mergeCell ref="B148:B151"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="D200:D203"/>
-    <mergeCell ref="F7:F10"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="E92:E95"/>
-    <mergeCell ref="D96:D99"/>
-    <mergeCell ref="B192:B195"/>
-    <mergeCell ref="B188:B191"/>
-    <mergeCell ref="E172:E175"/>
-    <mergeCell ref="F140:F143"/>
+    <mergeCell ref="E104:E107"/>
+    <mergeCell ref="A140:A143"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E144:E147"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="B39:B42"/>
     <mergeCell ref="F55:F58"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="F164:F167"/>
-    <mergeCell ref="D196:D199"/>
-    <mergeCell ref="E176:E179"/>
-    <mergeCell ref="F200:F203"/>
-    <mergeCell ref="C188:C191"/>
-    <mergeCell ref="E188:E191"/>
-    <mergeCell ref="F172:F175"/>
-    <mergeCell ref="C176:C179"/>
-    <mergeCell ref="A148:A151"/>
+    <mergeCell ref="F188:F191"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C148:C151"/>
+    <mergeCell ref="B116:B119"/>
+    <mergeCell ref="D116:D119"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="C132:C135"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="D152:D155"/>
     <mergeCell ref="F96:F99"/>
     <mergeCell ref="F152:F155"/>
+    <mergeCell ref="A100:A103"/>
     <mergeCell ref="C11:C14"/>
-    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C92:C95"/>
+    <mergeCell ref="F124:F127"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="E156:E159"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="D204:D207"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="C88:C91"/>
+    <mergeCell ref="E88:E91"/>
+    <mergeCell ref="E128:E131"/>
+    <mergeCell ref="E140:E143"/>
     <mergeCell ref="E11:E14"/>
-    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="E76:E79"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="E196:E199"/>
     <mergeCell ref="B80:B83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="E108:E111"/>
-    <mergeCell ref="F80:F83"/>
-    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="B192:B195"/>
+    <mergeCell ref="D172:D175"/>
+    <mergeCell ref="D192:D195"/>
+    <mergeCell ref="B144:B147"/>
+    <mergeCell ref="F136:F139"/>
+    <mergeCell ref="D88:D91"/>
     <mergeCell ref="D144:D147"/>
-    <mergeCell ref="F144:F147"/>
-    <mergeCell ref="E72:E75"/>
+    <mergeCell ref="B140:B143"/>
     <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E96:E99"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="F51:F54"/>
-    <mergeCell ref="B84:B87"/>
     <mergeCell ref="D140:D143"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C204:C207"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D59:D71"/>
+    <mergeCell ref="C108:C111"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="C160:C163"/>
+    <mergeCell ref="F196:F199"/>
+    <mergeCell ref="E55:E58"/>
     <mergeCell ref="F59:F71"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="C132:C135"/>
-    <mergeCell ref="C88:C91"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="A196:A199"/>
-    <mergeCell ref="C196:C199"/>
-    <mergeCell ref="D104:D107"/>
-    <mergeCell ref="E152:E155"/>
-    <mergeCell ref="E204:E207"/>
-    <mergeCell ref="B160:B163"/>
-    <mergeCell ref="A124:A127"/>
-    <mergeCell ref="A180:A183"/>
-    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="D124:D127"/>
     <mergeCell ref="F88:F91"/>
-    <mergeCell ref="C180:C183"/>
-    <mergeCell ref="F128:F131"/>
-    <mergeCell ref="F168:F171"/>
-    <mergeCell ref="B200:B203"/>
-    <mergeCell ref="D204:D207"/>
-    <mergeCell ref="A144:A147"/>
-    <mergeCell ref="B172:B175"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="D84:D87"/>
-    <mergeCell ref="E144:E147"/>
-    <mergeCell ref="D148:D151"/>
-    <mergeCell ref="C168:C171"/>
-    <mergeCell ref="C128:C131"/>
-    <mergeCell ref="A168:A171"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A59:A71"/>
+    <mergeCell ref="C140:C143"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B188:B191"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="E184:E187"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="E112:E115"/>
+    <mergeCell ref="E124:E127"/>
     <mergeCell ref="B156:B159"/>
-    <mergeCell ref="D156:D159"/>
-    <mergeCell ref="C59:C71"/>
-    <mergeCell ref="E59:E71"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="E148:E151"/>
-    <mergeCell ref="D168:D171"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="B144:B147"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="A96:A99"/>
-    <mergeCell ref="F148:F151"/>
-    <mergeCell ref="C152:C155"/>
-    <mergeCell ref="F100:F103"/>
-    <mergeCell ref="E128:E131"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="E47:E50"/>
-    <mergeCell ref="D76:D79"/>
-    <mergeCell ref="D116:D119"/>
-    <mergeCell ref="F76:F79"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="C148:C151"/>
-    <mergeCell ref="D31:D34"/>
-    <mergeCell ref="E55:E58"/>
-    <mergeCell ref="D72:D75"/>
-    <mergeCell ref="D128:D131"/>
-    <mergeCell ref="F72:F75"/>
-    <mergeCell ref="E136:E139"/>
-    <mergeCell ref="B208:B211"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="A116:A119"/>
-    <mergeCell ref="F15:F18"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B136:B139"/>
-    <mergeCell ref="D192:D195"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="F192:F195"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="B120:B123"/>
-    <mergeCell ref="E116:E119"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D120:D123"/>
-    <mergeCell ref="A59:A71"/>
-    <mergeCell ref="E156:E159"/>
-    <mergeCell ref="F176:F179"/>
-    <mergeCell ref="E208:E211"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="C136:C139"/>
-    <mergeCell ref="E200:E203"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="F124:F127"/>
-    <mergeCell ref="D164:D167"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="E132:E135"/>
-    <mergeCell ref="E88:E91"/>
-    <mergeCell ref="B180:B183"/>
-    <mergeCell ref="B196:B199"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="D152:D155"/>
-    <mergeCell ref="E184:E187"/>
-    <mergeCell ref="F31:F34"/>
-    <mergeCell ref="C172:C175"/>
-    <mergeCell ref="F47:F50"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="E51:E54"/>
-    <mergeCell ref="D92:D95"/>
-    <mergeCell ref="C96:C99"/>
-    <mergeCell ref="F92:F95"/>
-    <mergeCell ref="A184:A187"/>
-    <mergeCell ref="D180:D183"/>
-    <mergeCell ref="F2:F6"/>
-    <mergeCell ref="B59:B71"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="C144:C147"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C124:C127"/>
-    <mergeCell ref="E31:E34"/>
-    <mergeCell ref="C80:C83"/>
-    <mergeCell ref="E124:E127"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="E80:E83"/>
-    <mergeCell ref="F112:F115"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B168:B171"/>
     <mergeCell ref="E164:E167"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="C92:C95"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="B204:B207"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="D51:D54"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="A104:A107"/>
-    <mergeCell ref="B132:B135"/>
-    <mergeCell ref="F156:F159"/>
-    <mergeCell ref="E160:E163"/>
-    <mergeCell ref="D188:D191"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="F188:F191"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="F35:F38"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="E43:E46"/>
-    <mergeCell ref="F84:F87"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="B116:B119"/>
-    <mergeCell ref="E196:E199"/>
-    <mergeCell ref="C116:C119"/>
-    <mergeCell ref="E180:E183"/>
-    <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A160:A163"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="D108:D111"/>
-    <mergeCell ref="E76:E79"/>
-    <mergeCell ref="A112:A115"/>
-    <mergeCell ref="C112:C115"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="B140:B143"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="D47:D50"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="E84:E87"/>
-    <mergeCell ref="B88:B91"/>
-    <mergeCell ref="D88:D91"/>
-    <mergeCell ref="F136:F139"/>
-    <mergeCell ref="D176:D179"/>
-    <mergeCell ref="E100:E103"/>
-    <mergeCell ref="F120:F123"/>
-    <mergeCell ref="D160:D163"/>
-    <mergeCell ref="F160:F163"/>
-    <mergeCell ref="E168:E171"/>
-    <mergeCell ref="B176:B179"/>
-    <mergeCell ref="B128:B131"/>
-    <mergeCell ref="F104:F107"/>
-    <mergeCell ref="E120:E123"/>
-    <mergeCell ref="F108:F111"/>
-    <mergeCell ref="E140:E143"/>
-    <mergeCell ref="A128:A131"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C108:C111"/>
-    <mergeCell ref="C164:C167"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="E15:E18"/>
-    <mergeCell ref="A176:A179"/>
-    <mergeCell ref="E112:E115"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="A172:A175"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="D208:D211"/>
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="A156:A159"/>
-    <mergeCell ref="F208:F211"/>
-    <mergeCell ref="C156:C159"/>
-    <mergeCell ref="D184:D187"/>
-    <mergeCell ref="F184:F187"/>
-    <mergeCell ref="A188:A191"/>
-    <mergeCell ref="C104:C107"/>
-    <mergeCell ref="D136:D139"/>
-    <mergeCell ref="E104:E107"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>